--- a/InputData/indst/_cement/CSoIO/Cement Share of Industry 239 Output.xlsx
+++ b/InputData/indst/_cement/CSoIO/Cement Share of Industry 239 Output.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\indst\_cement\CSoIO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F684D78-9382-4611-8287-5280F3919176}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF3FC6A5-FEC8-43A7-A0AB-707A0A8D48BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -97,9 +97,6 @@
     <t>U.S. value</t>
   </si>
   <si>
-    <t>Share rounded to three decimals</t>
-  </si>
-  <si>
     <t>Unit: dimensionless</t>
   </si>
   <si>
@@ -152,7 +149,10 @@
 The 'Derivation' tab holds the inputs, the conversion to 2012 dollars, and the division, and the 'CSoIO' tab reads from it by formula and is what gets exported to CSoIO.csv.</t>
   </si>
   <si>
-    <t>Both numbers are in the model's 2012 dollars. The $16 billion of 2023 cement shipments becomes about $12.1 billion in 2012 dollars using the CPI-U, and dividing by $103.978 billion of modeled 2025 industry 239 output gives 0.116, rounded to three decimals. The two figures are two years apart; real growth in that span is small next to the rounding in the USGS value. We use the model's own industry 239 output rather than an outside total for nonmetallic minerals, because the outside totals include glass, which EPS carries as a separate industry (ISIC 231). The USGS value is rounded to the nearest billion, so the share is good to about two significant figures.</t>
+    <t>Cement share of industry 239 output</t>
+  </si>
+  <si>
+    <t>Both numbers are in the model's 2012 dollars. The $16 billion of 2023 cement shipments becomes about $12.1 billion in 2012 dollars using the CPI-U, and dividing by $103.978 billion of modeled 2025 industry 239 output gives 0.1159. The two figures are two years apart; real growth in that span is small next to the rounding in the USGS value. We use the model's own industry 239 output rather than an outside total for nonmetallic minerals, because the outside totals include glass, which EPS carries as a separate industry (ISIC 231). The USGS value is rounded to the nearest billion, so the share is good to about two significant figures.</t>
   </si>
 </sst>
 </file>
@@ -541,19 +541,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="2" max="2" width="110.7109375" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.6328125" customWidth="1"/>
+    <col min="2" max="2" width="110.6328125" customWidth="1"/>
+    <col min="3" max="3" width="3.6328125" customWidth="1"/>
+    <col min="4" max="4" width="9.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -561,105 +562,105 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B4" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B5" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B6" s="6">
         <v>2024</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B7" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="B8" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B10" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B11" s="6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="6" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B12" s="6" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B12" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B13" s="6">
         <v>2024</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B14" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="B15" s="6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="B15" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B18" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B19" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B20" s="6">
         <v>2026</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B21" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B22" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="135" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" ht="116" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="87" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>19</v>
       </c>
@@ -669,8 +670,8 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1" xr:uid="{6FB9079A-DD5E-4D73-BB5B-82233080BEE2}"/>
-    <hyperlink ref="B14" r:id="rId2" xr:uid="{A5832146-AC6C-470A-9D6D-3C190392936F}"/>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{A5ADB789-D8DA-4C16-B0ED-0368DE79A086}"/>
+    <hyperlink ref="B14" r:id="rId2" xr:uid="{D0D04B7F-36F9-4259-A1F1-E73C434383DD}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -679,14 +680,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -697,72 +698,72 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4">
         <v>16</v>
       </c>
       <c r="C4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>24</v>
       </c>
       <c r="B5">
         <v>229.59399999999999</v>
       </c>
       <c r="C5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>26</v>
       </c>
       <c r="B6">
         <v>304.702</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B7">
         <f>B4*B5/B6</f>
         <v>12.056054768265387</v>
       </c>
       <c r="C7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>29</v>
       </c>
       <c r="B8">
         <v>103.97799999999999</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
       <c r="B9">
-        <f>ROUND(B7/B8,3)</f>
-        <v>0.11600000000000001</v>
+        <f>(B7/B8)</f>
+        <v>0.11594813103026974</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -776,23 +777,23 @@
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2">
         <f>Derivation!B9</f>
-        <v>0.11600000000000001</v>
+        <v>0.11594813103026974</v>
       </c>
     </row>
   </sheetData>
